--- a/ig/ch-term/ValueSet-SubmissionSet.Author.AuthorRole.xlsx
+++ b/ig/ch-term/ValueSet-SubmissionSet.Author.AuthorRole.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
